--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY331"/>
+  <dimension ref="A1:AZ331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106191781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90906237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126779714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1175,6 +1195,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54634885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1411,6 +1441,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54634903</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1513,6 +1548,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66924218</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1625,6 +1665,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66924215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1745,6 +1790,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117025155</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1862,6 +1912,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471892</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1969,6 +2024,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449915</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2076,6 +2136,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114835303</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2179,6 +2244,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114835421</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2282,6 +2352,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114835654</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2403,6 +2478,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126779785</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2519,6 +2599,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253318</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2640,6 +2725,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253238</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2761,6 +2851,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253252</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2882,6 +2977,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130975673</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2998,6 +3098,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131344141</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3095,6 +3200,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80998430</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3195,6 +3305,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65078216</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3311,6 +3426,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126900760</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3408,6 +3528,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80999544</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3508,6 +3633,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65078188</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3608,6 +3738,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65078190</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3714,6 +3849,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129705431</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3811,6 +3951,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80998429</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3913,6 +4058,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126900729</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4010,6 +4160,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80998428</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4108,6 +4263,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126900755</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4228,6 +4388,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130975681</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4341,6 +4506,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104757120</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4441,6 +4611,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71853936</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4541,6 +4716,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71853928</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4641,6 +4821,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71853941</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4764,6 +4949,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024637</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4861,6 +5051,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129235361</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4958,6 +5153,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129235357</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5075,6 +5275,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246378</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5192,6 +5397,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246456</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5304,6 +5514,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246468</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5416,6 +5631,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132247045</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5528,6 +5748,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132247107</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5648,6 +5873,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127008489</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5760,6 +5990,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132248790</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5868,6 +6103,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56052585</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5977,6 +6217,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96338162</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6096,6 +6341,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125199174</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6208,6 +6458,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61806233</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6305,6 +6560,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80998462</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6402,6 +6662,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80998465</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6519,6 +6784,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487544</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6636,6 +6906,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131339176</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6753,6 +7028,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131443976</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6870,6 +7150,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444030</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6987,6 +7272,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444219</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7104,6 +7394,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131445377</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7220,6 +7515,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122193935</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7332,6 +7632,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129572834</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7453,6 +7758,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130988228</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7574,6 +7884,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131221364</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7686,6 +8001,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444592</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7817,6 +8137,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134515804</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7939,6 +8264,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444312</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8051,6 +8381,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338050</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8155,6 +8490,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99808209</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8267,6 +8607,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444123</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8379,6 +8724,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444353</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8491,6 +8841,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444376</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8603,6 +8958,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444818</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8715,6 +9075,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131445502</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8835,6 +9200,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901043</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8956,6 +9326,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545885</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9072,6 +9447,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545887</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9198,6 +9578,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545890</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9309,6 +9694,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026860</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9435,6 +9825,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074634</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9561,6 +9956,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074684</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9663,6 +10063,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95508045</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9783,6 +10188,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901057</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9899,6 +10309,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545888</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10016,6 +10431,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901550</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10114,6 +10534,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95045190</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10212,6 +10637,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060253</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10310,6 +10740,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060492</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10412,6 +10847,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060559</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10510,6 +10950,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060567</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10608,6 +11053,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060576</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10706,6 +11156,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95060610</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10804,6 +11259,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95508561</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10911,6 +11371,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054117</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11028,6 +11493,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054137</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11145,6 +11615,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054180</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11262,6 +11737,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054240</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11379,6 +11859,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054573</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11496,6 +11981,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054732</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11613,6 +12103,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054755</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11730,6 +12225,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054806</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11847,6 +12347,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074562</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11963,6 +12468,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545886</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12079,6 +12589,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545906</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12195,6 +12710,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545907</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12306,6 +12826,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026859</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12404,6 +12929,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114788849</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12525,6 +13055,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131469514</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12642,6 +13177,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545908</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12762,6 +13302,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545893</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12882,6 +13427,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545894</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13002,6 +13552,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545895</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13122,6 +13677,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545896</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13242,6 +13802,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545897</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13362,6 +13927,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545898</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13482,6 +14052,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545900</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13602,6 +14177,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545901</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13722,6 +14302,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545902</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13839,6 +14424,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545903</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13956,6 +14546,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545904</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14073,6 +14668,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545905</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14185,6 +14785,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074714</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14316,6 +14921,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545891</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14447,6 +15057,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341075</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14563,6 +15178,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131211950</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14675,6 +15295,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134524692</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14772,6 +15397,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81003109</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14869,6 +15499,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81003111</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14966,6 +15601,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81003113</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15085,6 +15725,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84572804</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15201,6 +15846,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297814</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15317,6 +15967,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129298159</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15429,6 +16084,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632161</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15541,6 +16201,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632227</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15658,6 +16323,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632255</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15775,6 +16445,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632345</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15899,6 +16574,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130773391</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16011,6 +16691,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132247532</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16131,6 +16816,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129790000</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16248,6 +16938,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358768</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16355,6 +17050,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851328</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16476,6 +17176,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131446798</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16578,6 +17283,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99613058</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16709,6 +17419,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130987668</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16826,6 +17541,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131849885</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16943,6 +17663,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850334</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17055,6 +17780,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850362</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17172,6 +17902,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850953</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17289,6 +18024,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894752</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17406,6 +18146,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010495</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17526,6 +18271,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129790204</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17646,6 +18396,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129790254</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17758,6 +18513,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98695496</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17870,6 +18630,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166532</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17986,6 +18751,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130987734</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18098,6 +18868,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850128</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18210,6 +18985,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852447</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18322,6 +19102,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853386</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18434,6 +19219,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853426</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18546,6 +19336,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853516</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18658,6 +19453,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853908</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18770,6 +19570,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853985</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18887,6 +19692,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854021</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18999,6 +19809,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854041</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19111,6 +19926,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854092</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19223,6 +20043,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854105</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19335,6 +20160,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854207</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19452,6 +20282,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894437</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19573,6 +20408,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894518</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19704,6 +20544,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894537</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19821,6 +20666,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894614</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19942,6 +20792,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009796</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20059,6 +20914,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009996</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20176,6 +21036,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010450</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20293,6 +21158,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010586</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20410,6 +21280,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010653</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20531,6 +21406,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133278755</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20648,6 +21528,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850501</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20765,6 +21650,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850830</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20882,6 +21772,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850864</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20999,6 +21894,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850707</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21116,6 +22016,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129370863</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21233,6 +22138,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129370752</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21345,6 +22255,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853986</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21462,6 +22377,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131850538</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21579,6 +22499,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894398</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21696,6 +22621,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894592</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21808,6 +22738,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131490836</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21945,6 +22880,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805528</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22063,6 +23003,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54920643</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22166,6 +23111,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134497665</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22288,6 +23238,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110222168</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22410,6 +23365,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110222188</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22527,6 +23487,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130987826</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22635,6 +23600,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56116532</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22743,6 +23713,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56116534</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22864,6 +23839,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490981</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22980,6 +23960,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491644</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23099,6 +24084,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129801551</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23218,6 +24208,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129801868</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23330,6 +24325,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803051</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23451,6 +24451,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803089</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23567,6 +24572,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803106</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23683,6 +24693,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803208</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23799,6 +24814,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803869</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23920,6 +24940,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803902</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24036,6 +25061,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803951</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24165,6 +25195,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132024009</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24294,6 +25329,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132024466</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24420,6 +25460,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132024564</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24528,6 +25573,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56116531</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24634,6 +25684,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152679</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24750,6 +25805,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491012</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24856,6 +25916,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803321</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24957,6 +26022,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113157618</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25073,6 +26143,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802891</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25180,6 +26255,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490880</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25292,6 +26372,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803419</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25404,6 +26489,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130502909</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25521,6 +26611,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129369795</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25643,6 +26738,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373684</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25760,6 +26860,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491220</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25877,6 +26982,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491760</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25994,6 +27104,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802014</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26106,6 +27221,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802131</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26218,6 +27338,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802241</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26330,6 +27455,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802893</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26447,6 +27577,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802916</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26559,6 +27694,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803004</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26671,6 +27811,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803135</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26773,6 +27918,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129804057</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26885,6 +28035,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920425</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26997,6 +28152,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920683</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27109,6 +28269,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129937873</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -27221,6 +28386,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129937960</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -27338,6 +28508,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972342</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27455,6 +28630,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972797</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27572,6 +28752,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972963</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27689,6 +28874,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973493</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27806,6 +28996,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973648</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27913,6 +29108,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130989062</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -28025,6 +29225,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131491162</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -28137,6 +29342,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131491205</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -28253,6 +29463,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131491876</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -28370,6 +29585,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011373</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28494,6 +29714,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129430626</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28614,6 +29839,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492527</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28731,6 +29961,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129801235</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28848,6 +30083,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803844</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28955,6 +30195,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803956</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -29072,6 +30317,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803968</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -29187,6 +30437,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129804046</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -29304,6 +30559,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972770</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -29424,6 +30684,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130978740</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29541,6 +30806,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130978837</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29660,6 +30930,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024764</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29783,6 +31058,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024797</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29900,6 +31180,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117141431</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -30009,6 +31294,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125199350</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -30126,6 +31416,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490876</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -30238,6 +31533,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491248</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -30354,6 +31654,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542168</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -30471,6 +31776,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574564</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -30597,6 +31907,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129784076</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -30728,6 +32043,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129790971</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30855,6 +32175,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129791065</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30971,6 +32296,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129791105</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -31081,6 +32411,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129796504</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -31203,6 +32538,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129796546</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -31319,6 +32659,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797343</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -31436,6 +32781,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129801508</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -31553,6 +32903,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803019</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -31665,6 +33020,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803057</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -31777,6 +33137,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884322</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31889,6 +33254,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129886500</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -32016,6 +33386,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972232</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -32128,6 +33503,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972605</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -32245,6 +33625,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973520</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -32371,6 +33756,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130976538</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -32488,6 +33878,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130976597</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -32609,6 +34004,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130978116</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -32730,6 +34130,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130978211</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -32847,6 +34252,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131221440</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32968,6 +34378,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131248983</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -33089,6 +34504,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131249118</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -33210,6 +34630,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253275</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -33331,6 +34756,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253282</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -33452,6 +34882,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253288</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -33573,6 +35008,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253289</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -33694,6 +35134,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131253291</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -33806,6 +35251,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131855640</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -33923,6 +35373,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131856296</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -34035,6 +35490,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131856764</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -34152,6 +35612,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131894283</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -34269,6 +35734,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011121</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -34386,6 +35856,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011265</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -34503,6 +35978,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011320</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -34620,6 +36100,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012314</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -34737,6 +36222,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013329</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -34854,6 +36344,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011568</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -34971,6 +36466,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130502888</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -35095,6 +36595,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130977946</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -35217,6 +36722,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920346</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -35339,6 +36849,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920477</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -35461,6 +36976,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920725</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -35574,6 +37094,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106172452</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -35691,6 +37216,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373608</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -35808,6 +37338,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397673</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -35927,6 +37462,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129802824</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -36049,6 +37589,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920387</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -36166,6 +37711,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920499</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -36283,6 +37833,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920541</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -36400,6 +37955,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920561</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -36517,6 +38077,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920764</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -36634,6 +38199,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920909</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -36751,6 +38321,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921044</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -36868,6 +38443,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921062</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -36985,6 +38565,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921480</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -37102,6 +38687,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934789</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -37219,6 +38809,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129937885</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -37336,6 +38931,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129937951</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -37455,6 +39055,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973016</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -37572,6 +39177,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129977870</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -37689,6 +39299,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013461</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -37801,6 +39416,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130988190</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -37916,6 +39536,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111914531</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -38027,6 +39652,11 @@
           <t>Groddjursinventering 1994 Örebro län</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/28786</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -38139,6 +39769,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123816436</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -38236,6 +39871,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803076</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -38353,6 +39993,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011491</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -38456,6 +40101,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77984560</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -38567,8 +40217,345 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/228867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>135471892</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135449915</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>135602704</v>
       </c>
       <c r="B66" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>135545885</v>
       </c>
       <c r="B76" t="n">
-        <v>93273</v>
+        <v>93315</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>135545887</v>
       </c>
       <c r="B77" t="n">
-        <v>93273</v>
+        <v>93315</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>135545890</v>
       </c>
       <c r="B78" t="n">
-        <v>92647</v>
+        <v>92689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>135545888</v>
       </c>
       <c r="B84" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>135545886</v>
       </c>
       <c r="B103" t="n">
-        <v>93289</v>
+        <v>93331</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>135545906</v>
       </c>
       <c r="B104" t="n">
-        <v>93289</v>
+        <v>93331</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>135545907</v>
       </c>
       <c r="B105" t="n">
-        <v>93289</v>
+        <v>93331</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>135545908</v>
       </c>
       <c r="B109" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>135545893</v>
       </c>
       <c r="B110" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135545894</v>
       </c>
       <c r="B111" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>135545895</v>
       </c>
       <c r="B112" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>135545896</v>
       </c>
       <c r="B113" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>135545897</v>
       </c>
       <c r="B114" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>135545898</v>
       </c>
       <c r="B115" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>135545900</v>
       </c>
       <c r="B116" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>135545901</v>
       </c>
       <c r="B117" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>135545902</v>
       </c>
       <c r="B118" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>135545903</v>
       </c>
       <c r="B119" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>135545904</v>
       </c>
       <c r="B120" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>135545905</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>135545891</v>
       </c>
       <c r="B123" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>135594287</v>
       </c>
       <c r="B189" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>135602697</v>
       </c>
       <c r="B196" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>135594540</v>
       </c>
       <c r="B302" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>135602700</v>
       </c>
       <c r="B303" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>135602699</v>
       </c>
       <c r="B328" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -1923,7 +1923,7 @@
         <v>135449915</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>135545885</v>
       </c>
       <c r="B76" t="n">
-        <v>93315</v>
+        <v>93342</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>135545887</v>
       </c>
       <c r="B77" t="n">
-        <v>93315</v>
+        <v>93342</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>135545890</v>
       </c>
       <c r="B78" t="n">
-        <v>92689</v>
+        <v>92716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>135545888</v>
       </c>
       <c r="B84" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>135545886</v>
       </c>
       <c r="B103" t="n">
-        <v>93331</v>
+        <v>93358</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>135545906</v>
       </c>
       <c r="B104" t="n">
-        <v>93331</v>
+        <v>93358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>135545907</v>
       </c>
       <c r="B105" t="n">
-        <v>93331</v>
+        <v>93358</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>135594287</v>
       </c>
       <c r="B189" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -3170,7 +3170,7 @@
         <v>135449915</v>
       </c>
       <c r="B22" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>135545885</v>
       </c>
       <c r="B86" t="n">
-        <v>93347</v>
+        <v>93349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>135545887</v>
       </c>
       <c r="B87" t="n">
-        <v>93347</v>
+        <v>93349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>135545890</v>
       </c>
       <c r="B88" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135545888</v>
       </c>
       <c r="B94" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135545886</v>
       </c>
       <c r="B113" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>135545906</v>
       </c>
       <c r="B114" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>135545907</v>
       </c>
       <c r="B115" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135594287</v>
       </c>
       <c r="B199" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>135452578</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135452579</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135452580</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135452581</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135452582</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135452583</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135452584</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>135452575</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135452576</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135452577</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135471892</v>
       </c>
       <c r="B21" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135449915</v>
       </c>
       <c r="B22" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>135602704</v>
       </c>
       <c r="B76" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>135545885</v>
       </c>
       <c r="B86" t="n">
-        <v>93349</v>
+        <v>93364</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>135545887</v>
       </c>
       <c r="B87" t="n">
-        <v>93349</v>
+        <v>93364</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>135545890</v>
       </c>
       <c r="B88" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135545888</v>
       </c>
       <c r="B94" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135545886</v>
       </c>
       <c r="B113" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>135545906</v>
       </c>
       <c r="B114" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>135545907</v>
       </c>
       <c r="B115" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>135545908</v>
       </c>
       <c r="B119" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>135545893</v>
       </c>
       <c r="B120" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>135545894</v>
       </c>
       <c r="B121" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>135545895</v>
       </c>
       <c r="B122" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>135545896</v>
       </c>
       <c r="B123" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>135545897</v>
       </c>
       <c r="B124" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>135545898</v>
       </c>
       <c r="B125" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>135545900</v>
       </c>
       <c r="B126" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135545901</v>
       </c>
       <c r="B127" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>135545902</v>
       </c>
       <c r="B128" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>135545903</v>
       </c>
       <c r="B129" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>135545904</v>
       </c>
       <c r="B130" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135545905</v>
       </c>
       <c r="B131" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>135545891</v>
       </c>
       <c r="B133" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135594287</v>
       </c>
       <c r="B199" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>135602697</v>
       </c>
       <c r="B206" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>135594540</v>
       </c>
       <c r="B312" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>135602700</v>
       </c>
       <c r="B313" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>135602699</v>
       </c>
       <c r="B338" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -10590,7 +10590,7 @@
         <v>135545885</v>
       </c>
       <c r="B86" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>135545887</v>
       </c>
       <c r="B87" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>135545890</v>
       </c>
       <c r="B88" t="n">
-        <v>92738</v>
+        <v>92739</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135545888</v>
       </c>
       <c r="B94" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135545886</v>
       </c>
       <c r="B113" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>135545906</v>
       </c>
       <c r="B114" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>135545907</v>
       </c>
       <c r="B115" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>135594287</v>
       </c>
       <c r="B199" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -24128,7 +24128,7 @@
         <v>135594287</v>
       </c>
       <c r="B199" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>135452578</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135452579</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135452580</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135452581</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135452582</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135452583</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135452584</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>135452575</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135452576</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135452577</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
